--- a/sampleprojects/SinusitisTherapy/excel/therapy.xlsx
+++ b/sampleprojects/SinusitisTherapy/excel/therapy.xlsx
@@ -8,13 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="Determine Therapy" sheetId="2" r:id="rId4"/>
+    <sheet name="Determine Creatinine Clearance" sheetId="3" r:id="rId6"/>
+    <sheet name="Determine Medication And Dosing" sheetId="4" r:id="rId7"/>
+    <sheet name="Select Medication" sheetId="5" r:id="rId8"/>
+    <sheet name="Determine Dose" sheetId="6" r:id="rId9"/>
+    <sheet name="Check Drug Interactions" sheetId="7" r:id="rId10"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>DT: Determine Therapy</t>
   </si>
@@ -49,40 +54,286 @@
     <t>Always run the full therapy workup</t>
   </si>
   <si>
+    <t>patient.diagnosis is equal to ignore case "Acute Sinusitis"</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>ACTIONS: COMMENTS</t>
+  </si>
+  <si>
+    <t>DSL: ACTIONS</t>
+  </si>
+  <si>
+    <t>Service 2 first: CCr feeds the dosing rules</t>
+  </si>
+  <si>
+    <t>perform Determine_Creatinine_Clearance</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Service 1: drug of choice and dosing</t>
+  </si>
+  <si>
+    <t>perform Determine_Medication_And_Dosing</t>
+  </si>
+  <si>
+    <t>Service 3: drug-interaction warnings</t>
+  </si>
+  <si>
+    <t>perform Check_Drug_Interactions</t>
+  </si>
+  <si>
+    <t>DT: Determine Creatinine Clearance</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 2000</t>
+  </si>
+  <si>
+    <t>Always compute CCr</t>
+  </si>
+  <si>
     <t>true</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>ACTIONS: COMMENTS</t>
-  </si>
-  <si>
-    <t>DSL: ACTIONS</t>
-  </si>
-  <si>
-    <t>Service 2 first: CCr feeds the dosing rules</t>
-  </si>
-  <si>
-    <t>perform Determine_Creatinine_Clearance</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Service 1: drug of choice and dosing</t>
-  </si>
-  <si>
-    <t>perform Determine_Medication_And_Dosing</t>
-  </si>
-  <si>
-    <t>Service 3: drug-interaction warnings</t>
-  </si>
-  <si>
-    <t>perform Check_Drug_Interactions</t>
+    <t>Cockcroft-Gault style: CCr = ((140 - age) * lean body weight) / (PCr * 72)</t>
+  </si>
+  <si>
+    <t>set result.ccr = ((140 - patient.age) * patient.lean_body_weight) / (patient.pcr * 72)</t>
+  </si>
+  <si>
+    <t>Rationale: CCr method</t>
+  </si>
+  <si>
+    <t>add "CCr estimated via Cockcroft-Gault from age, lean body weight, and plasma creatinine." to result.rationale</t>
+  </si>
+  <si>
+    <t>DT: Determine Medication And Dosing</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 3000</t>
+  </si>
+  <si>
+    <t>Always run</t>
+  </si>
+  <si>
+    <t>Pick the drug of choice</t>
+  </si>
+  <si>
+    <t>perform Select_Medication</t>
+  </si>
+  <si>
+    <t>Pick the dose / frequency / duration</t>
+  </si>
+  <si>
+    <t>perform Determine_Dose</t>
+  </si>
+  <si>
+    <t>DT: Select Medication</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 3010</t>
+  </si>
+  <si>
+    <t>Penicillin allergy overrides age (beta-lactam cross-reactivity)</t>
+  </si>
+  <si>
+    <t>patient.penicillin_allergic is true</t>
+  </si>
+  <si>
+    <t>Adult (&gt;= 18)</t>
+  </si>
+  <si>
+    <t>patient.age &gt;= constants.adult_age</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Fluoroquinolone for penicillin-allergic patients</t>
+  </si>
+  <si>
+    <t>set result.recommended_drug = "Levofloxacin"</t>
+  </si>
+  <si>
+    <t>Adult first-line</t>
+  </si>
+  <si>
+    <t>set result.recommended_drug = "Amoxicillin"</t>
+  </si>
+  <si>
+    <t>Pediatric first-line</t>
+  </si>
+  <si>
+    <t>set result.recommended_drug = "Cefuroxime"</t>
+  </si>
+  <si>
+    <t>Rationale: penicillin-allergic</t>
+  </si>
+  <si>
+    <t>add "Levofloxacin selected: fluoroquinolone avoids beta-lactam cross-reactivity in a penicillin-allergic patient." to result.rationale</t>
+  </si>
+  <si>
+    <t>Rationale: adult first-line</t>
+  </si>
+  <si>
+    <t>add "Amoxicillin selected: first-line beta-lactam for a non-allergic adult." to result.rationale</t>
+  </si>
+  <si>
+    <t>Rationale: pediatric first-line</t>
+  </si>
+  <si>
+    <t>add "Cefuroxime selected: first-line for a non-allergic pediatric patient." to result.rationale</t>
+  </si>
+  <si>
+    <t>DT: Determine Dose</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 3020</t>
+  </si>
+  <si>
+    <t>Renal impairment: PCr &gt; 1.4 and CCr &lt; 50</t>
+  </si>
+  <si>
+    <t>patient.pcr &gt; constants.renal_pcr_threshold and result.ccr &lt; constants.renal_ccr_threshold</t>
+  </si>
+  <si>
+    <t>Standard-dose age band (15..60)</t>
+  </si>
+  <si>
+    <t>patient.age &gt;= constants.dose_low_age and patient.age &lt;= constants.dose_high_age</t>
+  </si>
+  <si>
+    <t>Renal-reduced dose</t>
+  </si>
+  <si>
+    <t>set result.dose_mg = constants.reduced_dose</t>
+  </si>
+  <si>
+    <t>Standard dose for 15..60</t>
+  </si>
+  <si>
+    <t>set result.dose_mg = constants.standard_dose</t>
+  </si>
+  <si>
+    <t>Reduced dose for &lt;15 or &gt;60</t>
+  </si>
+  <si>
+    <t>Flag the renal adjustment</t>
+  </si>
+  <si>
+    <t>set result.renal_adjustment = true</t>
+  </si>
+  <si>
+    <t>Dosing interval (hours)</t>
+  </si>
+  <si>
+    <t>set result.frequency_hours = constants.dosing_interval_hours</t>
+  </si>
+  <si>
+    <t>Therapy duration (days)</t>
+  </si>
+  <si>
+    <t>set result.duration_days = constants.therapy_duration_days</t>
+  </si>
+  <si>
+    <t>DT: Check Drug Interactions</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 4000</t>
+  </si>
+  <si>
+    <t>for all patient.active_medications</t>
+  </si>
+  <si>
+    <t>Recommended drug is Levofloxacin</t>
+  </si>
+  <si>
+    <t>result.recommended_drug is equal to ignore case "Levofloxacin"</t>
+  </si>
+  <si>
+    <t>Recommended drug is Amoxicillin</t>
+  </si>
+  <si>
+    <t>result.recommended_drug is equal to ignore case "Amoxicillin"</t>
+  </si>
+  <si>
+    <t>Recommended drug is Cefuroxime</t>
+  </si>
+  <si>
+    <t>result.recommended_drug is equal to ignore case "Cefuroxime"</t>
+  </si>
+  <si>
+    <t>Active med is an anticoagulant</t>
+  </si>
+  <si>
+    <t>medication.name is equal to ignore case "Coumadin" or medication.name is equal to ignore case "Warfarin"</t>
+  </si>
+  <si>
+    <t>Active med is theophylline</t>
+  </si>
+  <si>
+    <t>medication.name is equal to ignore case "Theophylline"</t>
+  </si>
+  <si>
+    <t>Active med is an NSAID</t>
+  </si>
+  <si>
+    <t>medication.name is equal to ignore case "NSAID" or medication.name is equal to ignore case "Ibuprofen" or medication.name is equal to ignore case "Naproxen"</t>
+  </si>
+  <si>
+    <t>Active med is methotrexate</t>
+  </si>
+  <si>
+    <t>medication.name is equal to ignore case "Methotrexate"</t>
+  </si>
+  <si>
+    <t>Active med is probenecid</t>
+  </si>
+  <si>
+    <t>medication.name is equal to ignore case "Probenecid"</t>
+  </si>
+  <si>
+    <t>Levofloxacin + anticoagulant</t>
+  </si>
+  <si>
+    <t>add "Levofloxacin may potentiate the anticoagulant effect of warfarin/Coumadin, raising INR and bleeding risk. Monitor coagulation closely." to result.warnings</t>
+  </si>
+  <si>
+    <t>Levofloxacin + theophylline</t>
+  </si>
+  <si>
+    <t>add "Levofloxacin may increase theophylline plasma levels; monitor for theophylline toxicity." to result.warnings</t>
+  </si>
+  <si>
+    <t>Levofloxacin + NSAID</t>
+  </si>
+  <si>
+    <t>add "Concomitant NSAIDs with Levofloxacin may increase the risk of CNS stimulation and seizures." to result.warnings</t>
+  </si>
+  <si>
+    <t>Amoxicillin + anticoagulant</t>
+  </si>
+  <si>
+    <t>add "Amoxicillin may enhance the anticoagulant effect of warfarin/Coumadin; monitor INR." to result.warnings</t>
+  </si>
+  <si>
+    <t>Amoxicillin + methotrexate</t>
+  </si>
+  <si>
+    <t>add "Amoxicillin may reduce renal clearance of methotrexate, increasing methotrexate toxicity." to result.warnings</t>
+  </si>
+  <si>
+    <t>Cefuroxime + probenecid</t>
+  </si>
+  <si>
+    <t>add "Probenecid reduces renal excretion of Cefuroxime, raising its plasma concentration." to result.warnings</t>
   </si>
 </sst>
 </file>
@@ -957,4 +1208,3561 @@
     <mergeCell ref="A13:B13"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>9</v>
+      </c>
+      <c r="M10" s="1">
+        <v>10</v>
+      </c>
+      <c r="N10" s="1">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1">
+        <v>12</v>
+      </c>
+      <c r="P10" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>14</v>
+      </c>
+      <c r="R10" s="1">
+        <v>15</v>
+      </c>
+      <c r="S10" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>3</v>
+      </c>
+      <c r="G13" s="4">
+        <v>4</v>
+      </c>
+      <c r="H13" s="4">
+        <v>5</v>
+      </c>
+      <c r="I13" s="4">
+        <v>6</v>
+      </c>
+      <c r="J13" s="4">
+        <v>7</v>
+      </c>
+      <c r="K13" s="4">
+        <v>8</v>
+      </c>
+      <c r="L13" s="4">
+        <v>9</v>
+      </c>
+      <c r="M13" s="4">
+        <v>10</v>
+      </c>
+      <c r="N13" s="4">
+        <v>11</v>
+      </c>
+      <c r="O13" s="4">
+        <v>12</v>
+      </c>
+      <c r="P13" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>14</v>
+      </c>
+      <c r="R13" s="4">
+        <v>15</v>
+      </c>
+      <c r="S13" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:S8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>9</v>
+      </c>
+      <c r="M10" s="1">
+        <v>10</v>
+      </c>
+      <c r="N10" s="1">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1">
+        <v>12</v>
+      </c>
+      <c r="P10" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>14</v>
+      </c>
+      <c r="R10" s="1">
+        <v>15</v>
+      </c>
+      <c r="S10" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>3</v>
+      </c>
+      <c r="G13" s="4">
+        <v>4</v>
+      </c>
+      <c r="H13" s="4">
+        <v>5</v>
+      </c>
+      <c r="I13" s="4">
+        <v>6</v>
+      </c>
+      <c r="J13" s="4">
+        <v>7</v>
+      </c>
+      <c r="K13" s="4">
+        <v>8</v>
+      </c>
+      <c r="L13" s="4">
+        <v>9</v>
+      </c>
+      <c r="M13" s="4">
+        <v>10</v>
+      </c>
+      <c r="N13" s="4">
+        <v>11</v>
+      </c>
+      <c r="O13" s="4">
+        <v>12</v>
+      </c>
+      <c r="P13" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>14</v>
+      </c>
+      <c r="R13" s="4">
+        <v>15</v>
+      </c>
+      <c r="S13" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:S8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>9</v>
+      </c>
+      <c r="M10" s="1">
+        <v>10</v>
+      </c>
+      <c r="N10" s="1">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1">
+        <v>12</v>
+      </c>
+      <c r="P10" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>14</v>
+      </c>
+      <c r="R10" s="1">
+        <v>15</v>
+      </c>
+      <c r="S10" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>3</v>
+      </c>
+      <c r="G14" s="4">
+        <v>4</v>
+      </c>
+      <c r="H14" s="4">
+        <v>5</v>
+      </c>
+      <c r="I14" s="4">
+        <v>6</v>
+      </c>
+      <c r="J14" s="4">
+        <v>7</v>
+      </c>
+      <c r="K14" s="4">
+        <v>8</v>
+      </c>
+      <c r="L14" s="4">
+        <v>9</v>
+      </c>
+      <c r="M14" s="4">
+        <v>10</v>
+      </c>
+      <c r="N14" s="4">
+        <v>11</v>
+      </c>
+      <c r="O14" s="4">
+        <v>12</v>
+      </c>
+      <c r="P14" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>14</v>
+      </c>
+      <c r="R14" s="4">
+        <v>15</v>
+      </c>
+      <c r="S14" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
+        <v>3</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>5</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:S8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A14:B14"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>9</v>
+      </c>
+      <c r="M10" s="1">
+        <v>10</v>
+      </c>
+      <c r="N10" s="1">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1">
+        <v>12</v>
+      </c>
+      <c r="P10" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>14</v>
+      </c>
+      <c r="R10" s="1">
+        <v>15</v>
+      </c>
+      <c r="S10" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>3</v>
+      </c>
+      <c r="G14" s="4">
+        <v>4</v>
+      </c>
+      <c r="H14" s="4">
+        <v>5</v>
+      </c>
+      <c r="I14" s="4">
+        <v>6</v>
+      </c>
+      <c r="J14" s="4">
+        <v>7</v>
+      </c>
+      <c r="K14" s="4">
+        <v>8</v>
+      </c>
+      <c r="L14" s="4">
+        <v>9</v>
+      </c>
+      <c r="M14" s="4">
+        <v>10</v>
+      </c>
+      <c r="N14" s="4">
+        <v>11</v>
+      </c>
+      <c r="O14" s="4">
+        <v>12</v>
+      </c>
+      <c r="P14" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>14</v>
+      </c>
+      <c r="R14" s="4">
+        <v>15</v>
+      </c>
+      <c r="S14" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
+        <v>3</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>5</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:S8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A14:B14"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>7</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>8</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4">
+        <v>3</v>
+      </c>
+      <c r="G21" s="4">
+        <v>4</v>
+      </c>
+      <c r="H21" s="4">
+        <v>5</v>
+      </c>
+      <c r="I21" s="4">
+        <v>6</v>
+      </c>
+      <c r="J21" s="4">
+        <v>7</v>
+      </c>
+      <c r="K21" s="4">
+        <v>8</v>
+      </c>
+      <c r="L21" s="4">
+        <v>9</v>
+      </c>
+      <c r="M21" s="4">
+        <v>10</v>
+      </c>
+      <c r="N21" s="4">
+        <v>11</v>
+      </c>
+      <c r="O21" s="4">
+        <v>12</v>
+      </c>
+      <c r="P21" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>14</v>
+      </c>
+      <c r="R21" s="4">
+        <v>15</v>
+      </c>
+      <c r="S21" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>1</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
+        <v>2</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
+        <v>3</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A21:B21"/>
+  </mergeCells>
+</worksheet>
 </file>